--- a/part1_data_cleaning/outputs/data_quality_report.xlsx
+++ b/part1_data_cleaning/outputs/data_quality_report.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mitali Kalburgi\OneDrive\Desktop\Bitsom Notes\Assignments\Final Capstone Project\part1_data_cleaning\part1_data_cleaning\outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DDBAFB9-F798-4A2B-9DCD-FD2FDEDA1263}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C28E6ED0-73C8-4949-AB9C-6B6A762BDBFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11110" yWindow="0" windowWidth="11380" windowHeight="13370" firstSheet="6" activeTab="6" xr2:uid="{3B400EE0-56E2-4141-95E7-F5F2F0C5DF19}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" firstSheet="4" activeTab="6" xr2:uid="{3B400EE0-56E2-4141-95E7-F5F2F0C5DF19}"/>
   </bookViews>
   <sheets>
     <sheet name="duplicate_summary" sheetId="1" r:id="rId1"/>
@@ -332,9 +332,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="170" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -365,16 +365,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Carlito"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF244062"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -384,17 +395,105 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="1"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color theme="1"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color theme="1"/>
+        <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color theme="1"/>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -402,7 +501,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -411,55 +510,861 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="45">
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF244062"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF244062"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF244062"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF244062"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF244062"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF244062"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF244062"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -478,145 +1383,145 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C6DC73FE-267F-4DB8-82B8-2045AC37F6F9}" name="Table1" displayName="Table1" ref="A3:B9" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C6DC73FE-267F-4DB8-82B8-2045AC37F6F9}" name="Table1" displayName="Table1" ref="A3:B9" totalsRowShown="0" headerRowDxfId="41">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{5F0BDA3D-A7F7-4135-B414-ACF2AA245CF6}" name="Metric"/>
-    <tableColumn id="2" xr3:uid="{A5C65FD3-FF0D-4119-A2F5-8BC15FCFEF06}" name="Value"/>
+    <tableColumn id="1" xr3:uid="{5F0BDA3D-A7F7-4135-B414-ACF2AA245CF6}" name="Metric" dataDxfId="34"/>
+    <tableColumn id="2" xr3:uid="{A5C65FD3-FF0D-4119-A2F5-8BC15FCFEF06}" name="Value" dataDxfId="33"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{8FBFFD38-131E-4123-A572-3D35962ECF23}" name="Table11" displayName="Table11" ref="A3:B6" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{8FBFFD38-131E-4123-A572-3D35962ECF23}" name="Table11" displayName="Table11" ref="A3:B6" totalsRowShown="0" headerRowDxfId="36">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{7C8F33F3-0519-424F-A1A6-F98F77E2100F}" name="Metric"/>
-    <tableColumn id="2" xr3:uid="{A68B7E34-9753-415E-BCC5-AA27A958D089}" name="Count"/>
+    <tableColumn id="1" xr3:uid="{7C8F33F3-0519-424F-A1A6-F98F77E2100F}" name="Metric" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{A68B7E34-9753-415E-BCC5-AA27A958D089}" name="Count" dataDxfId="9"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{8F59FE74-A450-4B70-AC6C-3600BF33C98A}" name="Table12" displayName="Table12" ref="A10:B12" headerRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{8F59FE74-A450-4B70-AC6C-3600BF33C98A}" name="Table12" displayName="Table12" ref="A10:B12" headerRowCount="0" totalsRowShown="0" tableBorderDxfId="8">
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{031EB4A5-2140-4985-A904-A95A1C608773}" name="Column1"/>
-    <tableColumn id="2" xr3:uid="{AAAFAC26-0F2C-42E4-A201-8033B78BF645}" name="Column2" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{AAAFAC26-0F2C-42E4-A201-8033B78BF645}" name="Column2" dataDxfId="7"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{FF17E618-788A-46CB-8EA1-8E01A0089181}" name="Table13" displayName="Table13" ref="A16:B16" headerRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{FF17E618-788A-46CB-8EA1-8E01A0089181}" name="Table13" displayName="Table13" ref="A16:B16" headerRowCount="0" totalsRowShown="0" tableBorderDxfId="6">
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{C98DA26F-210A-45F5-8928-9BEA0D43BC7A}" name="Column1"/>
-    <tableColumn id="2" xr3:uid="{0CB9B59B-2FB0-4561-A1B0-4AC655354896}" name="Column2" headerRowDxfId="1" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{0CB9B59B-2FB0-4561-A1B0-4AC655354896}" name="Column2" headerRowDxfId="42" dataDxfId="5"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{A591CD3F-F58D-4B53-9869-6646CFF3F4D6}" name="Table14" displayName="Table14" ref="A3:C7" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{A591CD3F-F58D-4B53-9869-6646CFF3F4D6}" name="Table14" displayName="Table14" ref="A3:C7" totalsRowShown="0" headerRowDxfId="35">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{8EBCFC24-E945-4E4A-8602-1491A4A84519}" name="Status"/>
-    <tableColumn id="2" xr3:uid="{AA58DC5E-CE9E-401D-A944-E5F5AD432B0C}" name="Count"/>
-    <tableColumn id="3" xr3:uid="{9A127ED8-D613-47E9-81AF-360E32D5CD80}" name="Percentage" dataCellStyle="Percent"/>
+    <tableColumn id="1" xr3:uid="{8EBCFC24-E945-4E4A-8602-1491A4A84519}" name="Status" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{AA58DC5E-CE9E-401D-A944-E5F5AD432B0C}" name="Count" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{9A127ED8-D613-47E9-81AF-360E32D5CD80}" name="Percentage" dataDxfId="2" dataCellStyle="Percent"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{EB478BAC-7417-4E2E-8AEA-4141980C38FD}" name="Table15" displayName="Table15" ref="A11:B13" headerRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{EB478BAC-7417-4E2E-8AEA-4141980C38FD}" name="Table15" displayName="Table15" ref="A11:B13" headerRowCount="0" totalsRowShown="0" tableBorderDxfId="1">
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{7183A78C-A286-4B63-AE9A-78CCADDDF37E}" name="Column1"/>
     <tableColumn id="2" xr3:uid="{068B2213-0F62-46EB-8403-3382EA72F4D2}" name="Column2" dataDxfId="0"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BCABE7A8-FADE-47FC-9101-4C38176AB88C}" name="Table2" displayName="Table2" ref="A13:B14" headerRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BCABE7A8-FADE-47FC-9101-4C38176AB88C}" name="Table2" displayName="Table2" ref="A13:B14" headerRowCount="0" totalsRowShown="0" headerRowDxfId="28" tableBorderDxfId="32" totalsRowBorderDxfId="31">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{EF8EE78D-86E2-4CC6-B1CC-30ACAA4B29EC}" name="Logic"/>
-    <tableColumn id="2" xr3:uid="{36F845FE-A0A9-447B-A6E7-EDF9430CA484}" name="Explanation" headerRowDxfId="6" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{EF8EE78D-86E2-4CC6-B1CC-30ACAA4B29EC}" name="Logic" dataDxfId="30"/>
+    <tableColumn id="2" xr3:uid="{36F845FE-A0A9-447B-A6E7-EDF9430CA484}" name="Explanation" headerRowDxfId="44" dataDxfId="29"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{58CB44FE-0109-423D-8BB4-458C8C38F095}" name="Table3" displayName="Table3" ref="A3:C7" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{58CB44FE-0109-423D-8BB4-458C8C38F095}" name="Table3" displayName="Table3" ref="A3:C7" totalsRowShown="0" headerRowDxfId="40">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{49AB7867-A236-4136-AE93-1C045B2C5795}" name="Column"/>
-    <tableColumn id="2" xr3:uid="{985A8670-0029-4CC2-9712-8378DDCF0836}" name="Missing Count (Raw Data)"/>
-    <tableColumn id="3" xr3:uid="{89ECF86D-A160-4910-AC06-3F9A5E7BD133}" name="Action Taken" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{49AB7867-A236-4136-AE93-1C045B2C5795}" name="Column" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{985A8670-0029-4CC2-9712-8378DDCF0836}" name="Missing Count (Raw Data)" dataDxfId="26"/>
+    <tableColumn id="3" xr3:uid="{89ECF86D-A160-4910-AC06-3F9A5E7BD133}" name="Action Taken" dataDxfId="25"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{B5146FE8-FA83-4B09-B069-38FA5AFB3EC2}" name="Table5" displayName="Table5" ref="A3:B7" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{B5146FE8-FA83-4B09-B069-38FA5AFB3EC2}" name="Table5" displayName="Table5" ref="A3:B7" totalsRowShown="0" headerRowDxfId="39">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{354DEDCE-011A-41FF-8B7F-7193FCA34A3D}" name="Metric" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{A8A3F794-13A3-49CB-9383-62941808898C}" name="Count"/>
+    <tableColumn id="1" xr3:uid="{354DEDCE-011A-41FF-8B7F-7193FCA34A3D}" name="Metric" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{A8A3F794-13A3-49CB-9383-62941808898C}" name="Count" dataDxfId="18"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{1F3A82D0-7092-4EF0-A0A4-D300D9B1F5A9}" name="Table6" displayName="Table6" ref="A11:B13" headerRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{1F3A82D0-7092-4EF0-A0A4-D300D9B1F5A9}" name="Table6" displayName="Table6" ref="A11:B13" headerRowCount="0" totalsRowShown="0" headerRowDxfId="20" tableBorderDxfId="24" totalsRowBorderDxfId="23">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{1B31ABE2-9417-4A3A-8873-D2CD0B63D1ED}" name="Logic Used"/>
-    <tableColumn id="2" xr3:uid="{4BC6B7F0-350C-4FD9-8B45-AFEE21742C62}" name="Explanation" headerRowDxfId="5" dataDxfId="10"/>
+    <tableColumn id="1" xr3:uid="{1B31ABE2-9417-4A3A-8873-D2CD0B63D1ED}" name="Logic Used" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{4BC6B7F0-350C-4FD9-8B45-AFEE21742C62}" name="Explanation" headerRowDxfId="43" dataDxfId="21"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{048A8589-57FC-4F76-AC3E-B234E1D47E5F}" name="Table7" displayName="Table7" ref="A3:B7" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{048A8589-57FC-4F76-AC3E-B234E1D47E5F}" name="Table7" displayName="Table7" ref="A3:B7" totalsRowShown="0" headerRowDxfId="38">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{0C9828EA-4D84-4F06-A391-E574E6780FE2}" name="Metric" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{D211870B-0E54-4EEE-87E4-971D38A7145A}" name="Count"/>
+    <tableColumn id="1" xr3:uid="{0C9828EA-4D84-4F06-A391-E574E6780FE2}" name="Metric" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{D211870B-0E54-4EEE-87E4-971D38A7145A}" name="Count" dataDxfId="16"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{CEC7CB7D-44C7-484E-AEB4-CB25CB158E16}" name="Table8" displayName="Table8" ref="A11:B14" headerRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{CEC7CB7D-44C7-484E-AEB4-CB25CB158E16}" name="Table8" displayName="Table8" ref="A11:B14" headerRowCount="0" totalsRowShown="0" tableBorderDxfId="15">
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{058F2538-1816-462D-A69E-9BAE50A85283}" name="Column1"/>
     <tableColumn id="2" xr3:uid="{F5F438E1-8D7B-4EE3-8EB4-976789F18F93}" name="Column2"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{9F13E5C5-49A9-4904-BEDB-5FFFB3CF42D7}" name="Table9" displayName="Table9" ref="A18:B19" headerRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{9F13E5C5-49A9-4904-BEDB-5FFFB3CF42D7}" name="Table9" displayName="Table9" ref="A18:B19" headerRowCount="0" totalsRowShown="0" tableBorderDxfId="14">
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{CE1D6A84-C569-48D2-959B-091A7C677096}" name="Column1"/>
     <tableColumn id="2" xr3:uid="{DC2C9BCF-0851-410D-85E9-D8FAA539EE78}" name="Column2"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{DFB5BDD5-313A-46D4-8834-9A43FCF9569F}" name="Table10" displayName="Table10" ref="A3:C9" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{DFB5BDD5-313A-46D4-8834-9A43FCF9569F}" name="Table10" displayName="Table10" ref="A3:C9" totalsRowShown="0" headerRowDxfId="37">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{A9F18BCE-3019-4F79-B815-99A891DD2000}" name="Status Type"/>
-    <tableColumn id="2" xr3:uid="{C31104FB-231C-430A-9B81-191BC155FF47}" name="Count"/>
-    <tableColumn id="3" xr3:uid="{83C2D7B3-43FD-4C13-8C1A-5AB8E2A343ED}" name="Action Taken" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{A9F18BCE-3019-4F79-B815-99A891DD2000}" name="Status Type" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{C31104FB-231C-430A-9B81-191BC155FF47}" name="Count" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{83C2D7B3-43FD-4C13-8C1A-5AB8E2A343ED}" name="Action Taken" dataDxfId="11"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -917,93 +1822,92 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F15CB5CB-E6F6-4261-BF1D-37A4D7A22C12}">
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.7265625" customWidth="1"/>
     <col min="2" max="2" width="25.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:2" ht="21">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+    <row r="3" spans="1:2">
+      <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+    <row r="4" spans="1:2">
+      <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="5">
         <v>932</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+    <row r="5" spans="1:2">
+      <c r="A5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="5">
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+    <row r="6" spans="1:2">
+      <c r="A6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="5">
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+    <row r="7" spans="1:2">
+      <c r="A7" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="5">
         <v>912</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+    <row r="8" spans="1:2">
+      <c r="A8" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="5">
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+    <row r="9" spans="1:2">
+      <c r="A9" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="5">
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="21" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:2" ht="21">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="44" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" t="s">
+    <row r="13" spans="1:2" ht="43.5">
+      <c r="A13" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E13" s="7"/>
-    </row>
-    <row r="14" spans="1:5" ht="60.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+    </row>
+    <row r="14" spans="1:2" ht="60.5" customHeight="1">
+      <c r="A14" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="9" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1019,74 +1923,74 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD53535D-305F-476C-A540-2DD212A18A52}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="2" width="24.36328125" customWidth="1"/>
     <col min="3" max="3" width="13.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="30.5" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:3" ht="30.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3">
       <c r="A2" s="3"/>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+    <row r="3" spans="1:3" ht="28">
+      <c r="A3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="56.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+    <row r="4" spans="1:3" ht="56.5" customHeight="1">
+      <c r="A4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="5">
         <v>26</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="12" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="58" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+    <row r="5" spans="1:3" ht="58">
+      <c r="A5" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="5">
         <v>22</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="13" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="87" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+    <row r="6" spans="1:3" ht="87">
+      <c r="A6" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="5">
         <v>18</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="12" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+    <row r="7" spans="1:3" ht="29">
+      <c r="A7" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="5">
         <v>0</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="12" t="s">
         <v>24</v>
       </c>
     </row>
@@ -1101,83 +2005,83 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41BEA9AA-A400-45A1-BAB4-1154561F437B}">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="27.36328125" customWidth="1"/>
     <col min="2" max="2" width="28.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="21" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:2" ht="21">
       <c r="A1" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+    <row r="3" spans="1:2">
+      <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A4" s="6" t="s">
+    <row r="4" spans="1:2" ht="29">
+      <c r="A4" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="5">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="6" t="s">
+    <row r="5" spans="1:2">
+      <c r="A5" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="5">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A6" s="6" t="s">
+    <row r="6" spans="1:2" ht="29">
+      <c r="A6" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="5">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" s="6" t="s">
+    <row r="7" spans="1:2">
+      <c r="A7" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="5">
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="21" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:2" ht="21">
       <c r="A9" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+    <row r="11" spans="1:2" ht="43.5" customHeight="1">
+      <c r="A11" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="7" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+    <row r="12" spans="1:2" ht="43.5">
+      <c r="A12" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="15" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+    <row r="13" spans="1:2" ht="130.5">
+      <c r="A13" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="9" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1193,112 +2097,112 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0C2134B-8551-4F89-B05A-CEE8E29E03D4}">
   <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="22.90625" customWidth="1"/>
     <col min="2" max="2" width="24.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="21" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:2" ht="21">
       <c r="A1" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+    <row r="3" spans="1:2">
+      <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A4" s="5" t="s">
+    <row r="4" spans="1:2" ht="29">
+      <c r="A4" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="5" t="s">
+    <row r="5" spans="1:2" ht="43.5">
+      <c r="A5" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="5" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A6" s="5" t="s">
+    <row r="6" spans="1:2" ht="29">
+      <c r="A6" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="5" t="s">
+    <row r="7" spans="1:2" ht="43.5">
+      <c r="A7" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="5">
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="21" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:2" ht="21">
       <c r="A9" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+    <row r="11" spans="1:2">
+      <c r="A11" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="11" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" s="5" t="s">
+    <row r="12" spans="1:2">
+      <c r="A12" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="19" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A13" s="5" t="s">
+    <row r="13" spans="1:2" ht="29">
+      <c r="A13" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="19" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+    <row r="14" spans="1:2">
+      <c r="A14" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="10" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="21" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:2" ht="21">
       <c r="A16" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
+    <row r="18" spans="1:2">
+      <c r="A18" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="11" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
+    <row r="19" spans="1:2" ht="130.5">
+      <c r="A19" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="9" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1315,92 +2219,92 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF6D6D92-6B45-4AC8-86DD-6687B0478A63}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="15.1796875" customWidth="1"/>
     <col min="2" max="2" width="12.36328125" customWidth="1"/>
     <col min="3" max="3" width="20.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="21" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:3" ht="21">
       <c r="A1" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+    <row r="3" spans="1:3">
+      <c r="A3" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="58" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+    <row r="4" spans="1:3" ht="58">
+      <c r="A4" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="5">
         <v>145</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="17" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="58" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+    <row r="5" spans="1:3" ht="58">
+      <c r="A5" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="5">
         <v>37</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="17" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+    <row r="6" spans="1:3" ht="43.5">
+      <c r="A6" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="5">
         <v>34</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="13" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="5" t="s">
+    <row r="7" spans="1:3" ht="72.5">
+      <c r="A7" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="5">
         <v>24</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="13" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="5" t="s">
+    <row r="8" spans="1:3" ht="43.5">
+      <c r="A8" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="5">
         <v>240</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="17" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A9" s="5" t="s">
+    <row r="9" spans="1:3" ht="29">
+      <c r="A9" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="5">
         <v>672</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="13" t="s">
         <v>70</v>
       </c>
     </row>
@@ -1415,88 +2319,88 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E6FDD5E-11E4-44F0-9DFC-E17AA709DCCD}">
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="23.36328125" customWidth="1"/>
     <col min="2" max="2" width="16.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="21" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:2" ht="21">
       <c r="A1" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+    <row r="3" spans="1:2">
+      <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+    <row r="4" spans="1:2">
+      <c r="A4" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="5">
         <v>912</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A5" s="5" t="s">
+    <row r="5" spans="1:2" ht="29">
+      <c r="A5" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="5">
         <v>93</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A6" s="5" t="s">
+    <row r="6" spans="1:2" ht="29">
+      <c r="A6" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="5">
         <v>94</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="21" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:2" ht="21">
       <c r="A8" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+    <row r="10" spans="1:2" ht="43.5">
+      <c r="A10" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="7" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+    <row r="11" spans="1:2" ht="29">
+      <c r="A11" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="20" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+    <row r="12" spans="1:2" ht="130.5">
+      <c r="A12" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="21" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="21" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:2" ht="21">
       <c r="A14" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="174" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
+    <row r="16" spans="1:2" ht="174">
+      <c r="A16" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="22" t="s">
         <v>83</v>
       </c>
     </row>
@@ -1513,99 +2417,99 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F354AFB8-0AE5-4297-A26D-4C3774698FC1}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="20.54296875" customWidth="1"/>
     <col min="3" max="3" width="15.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="21" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:3" ht="21">
       <c r="A1" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+    <row r="3" spans="1:3">
+      <c r="A3" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="4" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+    <row r="4" spans="1:3">
+      <c r="A4" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="5">
         <v>643</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="23">
         <v>0.70499999999999996</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+    <row r="5" spans="1:3">
+      <c r="A5" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="5">
         <v>218</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="23">
         <v>0.23899999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+    <row r="6" spans="1:3">
+      <c r="A6" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="5">
         <v>51</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="23">
         <v>5.6000000000000001E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+    <row r="7" spans="1:3">
+      <c r="A7" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="5">
         <v>912</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="23">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="21" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:3" ht="21">
       <c r="A9" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="87" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+    <row r="11" spans="1:3" ht="87">
+      <c r="A11" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="24" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+    <row r="12" spans="1:3" ht="101.5">
+      <c r="A12" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="20" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+    <row r="13" spans="1:3" ht="72.5">
+      <c r="A13" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="21" t="s">
         <v>94</v>
       </c>
     </row>
